--- a/Imports/modeles/Prefixes.xlsx
+++ b/Imports/modeles/Prefixes.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Prefixes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prefixes" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -423,12 +423,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -439,11 +438,6 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Axe</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
           <t>Libellé</t>
         </is>
       </c>
